--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92568406799</v>
+        <v>46157.93097925327</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93097925327</v>
+        <v>46157.9317307118</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9317307118</v>
+        <v>46157.93400219749</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93400219749</v>
+        <v>46157.93718105439</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718105439</v>
+        <v>46158.28216434643</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216434643</v>
+        <v>46158.29681664496</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29681664496</v>
+        <v>46158.29814835653</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814835653</v>
+        <v>46158.33387518825</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387518825</v>
+        <v>46158.36857263661</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36857263661</v>
+        <v>46158.3728794938</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
